--- a/Reporte_Personas.xlsx
+++ b/Reporte_Personas.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="11">
   <si>
     <t>Nombre</t>
   </si>
@@ -34,103 +34,19 @@
     <t>Fecha Entrega</t>
   </si>
   <si>
+    <t>edgar</t>
+  </si>
+  <si>
+    <t>123</t>
+  </si>
+  <si>
+    <t>sda</t>
+  </si>
+  <si>
     <t>asd</t>
   </si>
   <si>
-    <t>sadas</t>
-  </si>
-  <si>
-    <t>dsad</t>
-  </si>
-  <si>
-    <t>dasas</t>
-  </si>
-  <si>
-    <t>asdas</t>
-  </si>
-  <si>
-    <t>asda</t>
-  </si>
-  <si>
-    <t>asdasd</t>
-  </si>
-  <si>
-    <t>dasdas</t>
-  </si>
-  <si>
-    <t>das</t>
-  </si>
-  <si>
-    <t xml:space="preserve">paolito </t>
-  </si>
-  <si>
-    <t>929</t>
-  </si>
-  <si>
-    <t>9923</t>
-  </si>
-  <si>
-    <t>9291</t>
-  </si>
-  <si>
-    <t>lweqk</t>
-  </si>
-  <si>
-    <t>012'3</t>
-  </si>
-  <si>
-    <t>montemorelos</t>
-  </si>
-  <si>
-    <t>paolito adasd</t>
-  </si>
-  <si>
-    <t>sadasd</t>
-  </si>
-  <si>
-    <t>asdasdas</t>
-  </si>
-  <si>
-    <t>dasdasd</t>
-  </si>
-  <si>
-    <t>dasd</t>
-  </si>
-  <si>
-    <t>ulti</t>
-  </si>
-  <si>
-    <t>dulti</t>
-  </si>
-  <si>
-    <t>asdasdulti</t>
-  </si>
-  <si>
-    <t>asdulti</t>
-  </si>
-  <si>
-    <t>asdasulti</t>
-  </si>
-  <si>
-    <t xml:space="preserve">vi </t>
-  </si>
-  <si>
-    <t>oiasdjo</t>
-  </si>
-  <si>
-    <t>poskpwodk</t>
-  </si>
-  <si>
-    <t>dsapk</t>
-  </si>
-  <si>
-    <t>dpasokpo</t>
-  </si>
-  <si>
-    <t>dápw</t>
-  </si>
-  <si>
-    <t>zz</t>
+    <t>ads</t>
   </si>
 </sst>
 </file>
@@ -178,8 +94,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:F11" totalsRowShown="0">
-  <autoFilter ref="A1:F11"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:F2" totalsRowShown="0">
+  <autoFilter ref="A1:F2"/>
   <tableColumns count="6">
     <tableColumn id="1" name="Nombre"/>
     <tableColumn id="2" name="Teléfono"/>
@@ -477,13 +393,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="15.7109375" customWidth="1"/>
+    <col min="1" max="1" width="8.7109375" customWidth="1"/>
     <col min="2" max="2" width="10.7109375" customWidth="1"/>
-    <col min="3" max="3" width="11.7109375" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" customWidth="1"/>
+    <col min="3" max="4" width="11.7109375" customWidth="1"/>
     <col min="5" max="5" width="16.7109375" customWidth="1"/>
     <col min="6" max="6" width="15.7109375" customWidth="1"/>
   </cols>
@@ -525,187 +440,7 @@
         <v>10</v>
       </c>
       <c r="F2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" t="s">
         <v>9</v>
-      </c>
-      <c r="E3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" t="s">
-        <v>13</v>
-      </c>
-      <c r="D4" t="s">
-        <v>13</v>
-      </c>
-      <c r="E4" t="s">
-        <v>14</v>
-      </c>
-      <c r="F4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C5" t="s">
-        <v>17</v>
-      </c>
-      <c r="D5" t="s">
-        <v>18</v>
-      </c>
-      <c r="E5" t="s">
-        <v>19</v>
-      </c>
-      <c r="F5" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" t="s">
-        <v>15</v>
-      </c>
-      <c r="B6" t="s">
-        <v>16</v>
-      </c>
-      <c r="C6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E6" t="s">
-        <v>19</v>
-      </c>
-      <c r="F6" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" t="s">
-        <v>22</v>
-      </c>
-      <c r="B7" t="s">
-        <v>16</v>
-      </c>
-      <c r="C7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D7" t="s">
-        <v>18</v>
-      </c>
-      <c r="E7" t="s">
-        <v>19</v>
-      </c>
-      <c r="F7" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" t="s">
-        <v>23</v>
-      </c>
-      <c r="B8" t="s">
-        <v>24</v>
-      </c>
-      <c r="C8" t="s">
-        <v>25</v>
-      </c>
-      <c r="D8" t="s">
-        <v>10</v>
-      </c>
-      <c r="E8" t="s">
-        <v>10</v>
-      </c>
-      <c r="F8" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" t="s">
-        <v>27</v>
-      </c>
-      <c r="B9" t="s">
-        <v>27</v>
-      </c>
-      <c r="C9" t="s">
-        <v>28</v>
-      </c>
-      <c r="D9" t="s">
-        <v>29</v>
-      </c>
-      <c r="E9" t="s">
-        <v>30</v>
-      </c>
-      <c r="F9" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" t="s">
-        <v>32</v>
-      </c>
-      <c r="B10" t="s">
-        <v>33</v>
-      </c>
-      <c r="C10" t="s">
-        <v>34</v>
-      </c>
-      <c r="D10" t="s">
-        <v>35</v>
-      </c>
-      <c r="E10" t="s">
-        <v>36</v>
-      </c>
-      <c r="F10" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" t="s">
-        <v>38</v>
-      </c>
-      <c r="B11" t="s">
-        <v>27</v>
-      </c>
-      <c r="C11" t="s">
-        <v>28</v>
-      </c>
-      <c r="D11" t="s">
-        <v>29</v>
-      </c>
-      <c r="E11" t="s">
-        <v>30</v>
-      </c>
-      <c r="F11" t="s">
-        <v>31</v>
       </c>
     </row>
   </sheetData>

--- a/Reporte_Personas.xlsx
+++ b/Reporte_Personas.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="17">
   <si>
     <t>Nombre</t>
   </si>
@@ -32,6 +32,24 @@
   </si>
   <si>
     <t>Fecha Entrega</t>
+  </si>
+  <si>
+    <t>ed</t>
+  </si>
+  <si>
+    <t>rd</t>
+  </si>
+  <si>
+    <t>gf</t>
+  </si>
+  <si>
+    <t>hgv</t>
+  </si>
+  <si>
+    <t>2025-01-08</t>
+  </si>
+  <si>
+    <t>2026-02-09</t>
   </si>
   <si>
     <t>edgar</t>
@@ -94,8 +112,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:F2" totalsRowShown="0">
-  <autoFilter ref="A1:F2"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:F3" totalsRowShown="0">
+  <autoFilter ref="A1:F3"/>
   <tableColumns count="6">
     <tableColumn id="1" name="Nombre"/>
     <tableColumn id="2" name="Teléfono"/>
@@ -393,7 +411,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="8.7109375" customWidth="1"/>
@@ -440,7 +458,27 @@
         <v>10</v>
       </c>
       <c r="F2" t="s">
-        <v>9</v>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F3" t="s">
+        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/Reporte_Personas.xlsx
+++ b/Reporte_Personas.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="14">
   <si>
     <t>Nombre</t>
   </si>
@@ -34,76 +34,28 @@
     <t>Fecha Entrega</t>
   </si>
   <si>
-    <t>nuevo</t>
-  </si>
-  <si>
-    <t>123123</t>
-  </si>
-  <si>
-    <t>12312</t>
-  </si>
-  <si>
-    <t>2025-01-12</t>
-  </si>
-  <si>
-    <t>qwe</t>
-  </si>
-  <si>
-    <t>wqe</t>
-  </si>
-  <si>
-    <t>Linares</t>
+    <t>12</t>
+  </si>
+  <si>
+    <t>123</t>
+  </si>
+  <si>
+    <t>Rayones</t>
+  </si>
+  <si>
+    <t>2025-01-07</t>
+  </si>
+  <si>
+    <t>234</t>
+  </si>
+  <si>
+    <t>324</t>
+  </si>
+  <si>
+    <t>Hualahuises</t>
   </si>
   <si>
     <t>2025-01-13</t>
-  </si>
-  <si>
-    <t>sadas</t>
-  </si>
-  <si>
-    <t>asdas</t>
-  </si>
-  <si>
-    <t>Allende</t>
-  </si>
-  <si>
-    <t>sadasd</t>
-  </si>
-  <si>
-    <t>asd</t>
-  </si>
-  <si>
-    <t>sad</t>
-  </si>
-  <si>
-    <t>Rayones</t>
-  </si>
-  <si>
-    <t>sd</t>
-  </si>
-  <si>
-    <t>assd</t>
-  </si>
-  <si>
-    <t>asdasd</t>
-  </si>
-  <si>
-    <t>sdf</t>
-  </si>
-  <si>
-    <t>sdfsdf</t>
-  </si>
-  <si>
-    <t>sdfs</t>
-  </si>
-  <si>
-    <t>sfd</t>
-  </si>
-  <si>
-    <t>vs</t>
-  </si>
-  <si>
-    <t>Montemorelos</t>
   </si>
 </sst>
 </file>
@@ -151,8 +103,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:F9" totalsRowShown="0">
-  <autoFilter ref="A1:F9"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:F3" totalsRowShown="0">
+  <autoFilter ref="A1:F3"/>
   <tableColumns count="6">
     <tableColumn id="1" name="Nombre"/>
     <tableColumn id="2" name="Teléfono"/>
@@ -450,13 +402,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="8.7109375" customWidth="1"/>
     <col min="2" max="2" width="10.7109375" customWidth="1"/>
     <col min="3" max="3" width="11.7109375" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" customWidth="1"/>
+    <col min="4" max="4" width="13.7109375" customWidth="1"/>
     <col min="5" max="5" width="16.7109375" customWidth="1"/>
     <col min="6" max="6" width="15.7109375" customWidth="1"/>
   </cols>
@@ -489,15 +441,12 @@
         <v>7</v>
       </c>
       <c r="C2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D2" t="s">
         <v>8</v>
       </c>
       <c r="E2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" t="s">
         <v>9</v>
       </c>
     </row>
@@ -516,120 +465,6 @@
       </c>
       <c r="E3" t="s">
         <v>13</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D4" t="s">
-        <v>16</v>
-      </c>
-      <c r="E4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" t="s">
-        <v>17</v>
-      </c>
-      <c r="B5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C5" t="s">
-        <v>19</v>
-      </c>
-      <c r="D5" t="s">
-        <v>20</v>
-      </c>
-      <c r="E5" t="s">
-        <v>13</v>
-      </c>
-      <c r="F5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" t="s">
-        <v>21</v>
-      </c>
-      <c r="B6" t="s">
-        <v>22</v>
-      </c>
-      <c r="C6" t="s">
-        <v>23</v>
-      </c>
-      <c r="D6" t="s">
-        <v>12</v>
-      </c>
-      <c r="E6" t="s">
-        <v>9</v>
-      </c>
-      <c r="F6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" t="s">
-        <v>24</v>
-      </c>
-      <c r="B7" t="s">
-        <v>25</v>
-      </c>
-      <c r="C7" t="s">
-        <v>26</v>
-      </c>
-      <c r="D7" t="s">
-        <v>27</v>
-      </c>
-      <c r="E7" t="s">
-        <v>9</v>
-      </c>
-      <c r="F7" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" t="s">
-        <v>28</v>
-      </c>
-      <c r="B8" t="s">
-        <v>24</v>
-      </c>
-      <c r="C8" t="s">
-        <v>24</v>
-      </c>
-      <c r="D8" t="s">
-        <v>24</v>
-      </c>
-      <c r="E8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F8" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" t="s">
-        <v>11</v>
-      </c>
-      <c r="B9" t="s">
-        <v>10</v>
-      </c>
-      <c r="C9" t="s">
-        <v>11</v>
-      </c>
-      <c r="D9" t="s">
-        <v>29</v>
-      </c>
-      <c r="E9" t="s">
-        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/Reporte_Personas.xlsx
+++ b/Reporte_Personas.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="15">
   <si>
     <t>Nombre</t>
   </si>
@@ -34,28 +34,31 @@
     <t>Fecha Entrega</t>
   </si>
   <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>123</t>
+    <t>Alan</t>
+  </si>
+  <si>
+    <t>213123123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Los Nogales 213 </t>
   </si>
   <si>
     <t>Rayones</t>
   </si>
   <si>
-    <t>2025-01-07</t>
-  </si>
-  <si>
-    <t>234</t>
-  </si>
-  <si>
-    <t>324</t>
-  </si>
-  <si>
-    <t>Hualahuises</t>
-  </si>
-  <si>
     <t>2025-01-13</t>
+  </si>
+  <si>
+    <t>Edgar</t>
+  </si>
+  <si>
+    <t>123213</t>
+  </si>
+  <si>
+    <t>Centro 213</t>
+  </si>
+  <si>
+    <t>Montemorelos</t>
   </si>
 </sst>
 </file>
@@ -406,9 +409,9 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="8.7109375" customWidth="1"/>
-    <col min="2" max="2" width="10.7109375" customWidth="1"/>
-    <col min="3" max="3" width="11.7109375" customWidth="1"/>
-    <col min="4" max="4" width="13.7109375" customWidth="1"/>
+    <col min="2" max="2" width="11.7109375" customWidth="1"/>
+    <col min="3" max="3" width="18.7109375" customWidth="1"/>
+    <col min="4" max="4" width="14.7109375" customWidth="1"/>
     <col min="5" max="5" width="16.7109375" customWidth="1"/>
     <col min="6" max="6" width="15.7109375" customWidth="1"/>
   </cols>
@@ -441,30 +444,33 @@
         <v>7</v>
       </c>
       <c r="C2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E2" t="s">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="F2" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" t="s">
         <v>10</v>
-      </c>
-      <c r="B3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" t="s">
-        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/Reporte_Personas.xlsx
+++ b/Reporte_Personas.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="23">
   <si>
     <t>Nombre</t>
   </si>
@@ -34,7 +34,7 @@
     <t>Fecha Entrega</t>
   </si>
   <si>
-    <t>Alan</t>
+    <t>Alana</t>
   </si>
   <si>
     <t>213123123</t>
@@ -59,6 +59,30 @@
   </si>
   <si>
     <t>Montemorelos</t>
+  </si>
+  <si>
+    <t>asd</t>
+  </si>
+  <si>
+    <t>12312</t>
+  </si>
+  <si>
+    <t>dasas</t>
+  </si>
+  <si>
+    <t>2025-01-15</t>
+  </si>
+  <si>
+    <t>2025-01-22</t>
+  </si>
+  <si>
+    <t>asdas</t>
+  </si>
+  <si>
+    <t>12asd</t>
+  </si>
+  <si>
+    <t>Linares</t>
   </si>
 </sst>
 </file>
@@ -106,8 +130,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:F3" totalsRowShown="0">
-  <autoFilter ref="A1:F3"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:F5" totalsRowShown="0">
+  <autoFilter ref="A1:F5"/>
   <tableColumns count="6">
     <tableColumn id="1" name="Nombre"/>
     <tableColumn id="2" name="Teléfono"/>
@@ -405,7 +429,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="8.7109375" customWidth="1"/>
@@ -452,9 +476,6 @@
       <c r="E2" t="s">
         <v>10</v>
       </c>
-      <c r="F2" t="s">
-        <v>10</v>
-      </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" t="s">
@@ -471,6 +492,46 @@
       </c>
       <c r="E3" t="s">
         <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D5" t="s">
+        <v>22</v>
+      </c>
+      <c r="E5" t="s">
+        <v>18</v>
+      </c>
+      <c r="F5" t="s">
+        <v>18</v>
       </c>
     </row>
   </sheetData>

--- a/Reporte_Personas.xlsx
+++ b/Reporte_Personas.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="32">
   <si>
     <t>Nombre</t>
   </si>
@@ -34,7 +34,7 @@
     <t>Fecha Entrega</t>
   </si>
   <si>
-    <t>Alana</t>
+    <t>Alan</t>
   </si>
   <si>
     <t>213123123</t>
@@ -49,6 +49,9 @@
     <t>2025-01-13</t>
   </si>
   <si>
+    <t>2025-01-30</t>
+  </si>
+  <si>
     <t>Edgar</t>
   </si>
   <si>
@@ -61,28 +64,52 @@
     <t>Montemorelos</t>
   </si>
   <si>
-    <t>asd</t>
+    <t>Ramon</t>
+  </si>
+  <si>
+    <t>21301203</t>
   </si>
   <si>
     <t>12312</t>
   </si>
   <si>
-    <t>dasas</t>
+    <t>2025-01-16</t>
+  </si>
+  <si>
+    <t>adan</t>
+  </si>
+  <si>
+    <t>213312</t>
+  </si>
+  <si>
+    <t>dasd</t>
+  </si>
+  <si>
+    <t>Hualahuises</t>
+  </si>
+  <si>
+    <t>asdas</t>
+  </si>
+  <si>
+    <t>12asd</t>
+  </si>
+  <si>
+    <t>Linares</t>
   </si>
   <si>
     <t>2025-01-15</t>
   </si>
   <si>
-    <t>2025-01-22</t>
-  </si>
-  <si>
-    <t>asdas</t>
-  </si>
-  <si>
-    <t>12asd</t>
-  </si>
-  <si>
-    <t>Linares</t>
+    <t>cas</t>
+  </si>
+  <si>
+    <t>21312</t>
+  </si>
+  <si>
+    <t>dsads</t>
+  </si>
+  <si>
+    <t>2025-01-24</t>
   </si>
 </sst>
 </file>
@@ -130,8 +157,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:F5" totalsRowShown="0">
-  <autoFilter ref="A1:F5"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:F7" totalsRowShown="0">
+  <autoFilter ref="A1:F7"/>
   <tableColumns count="6">
     <tableColumn id="1" name="Nombre"/>
     <tableColumn id="2" name="Teléfono"/>
@@ -429,7 +456,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="8.7109375" customWidth="1"/>
@@ -476,19 +503,22 @@
       <c r="E2" t="s">
         <v>10</v>
       </c>
+      <c r="F2" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
@@ -496,19 +526,19 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D4" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F4" t="s">
         <v>19</v>
@@ -519,19 +549,50 @@
         <v>20</v>
       </c>
       <c r="B5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E5" t="s">
-        <v>18</v>
-      </c>
-      <c r="F5" t="s">
-        <v>18</v>
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" t="s">
+        <v>24</v>
+      </c>
+      <c r="B6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" t="s">
+        <v>25</v>
+      </c>
+      <c r="D6" t="s">
+        <v>26</v>
+      </c>
+      <c r="E6" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" t="s">
+        <v>28</v>
+      </c>
+      <c r="B7" t="s">
+        <v>29</v>
+      </c>
+      <c r="C7" t="s">
+        <v>30</v>
+      </c>
+      <c r="D7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E7" t="s">
+        <v>31</v>
       </c>
     </row>
   </sheetData>
